--- a/Adresses.xlsx
+++ b/Adresses.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="98" documentId="11_F25DC773A252ABDACC1048FE015D5EC65ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7441DB63-8556-427E-8ACA-33314E385614}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1730" yWindow="880" windowWidth="14400" windowHeight="7280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Adresses.xlsx
+++ b/Adresses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://magals3-my.sharepoint.com/personal/elishamaa_magalsolutions_com/Documents/Desktop/Project/Github/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="11_F25DC773A252ABDACC1048FE015D5EC65ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7441DB63-8556-427E-8ACA-33314E385614}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="11_F25DC773A252ABDACC1048FE015D5EC65ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20BFF49D-CD3B-4037-8B9E-175540AD8759}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
   <si>
     <t>Router-BR-1</t>
   </si>
@@ -162,7 +162,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -170,12 +170,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,209 +476,260 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E9" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E11" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E12" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E14" t="s">
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E15" t="s">
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E16" t="s">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E17" t="s">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E18" t="s">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
